--- a/artfynd/A 59665-2022 artfynd.xlsx
+++ b/artfynd/A 59665-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59665-2022 artfynd.xlsx
+++ b/artfynd/A 59665-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110216939</v>
+        <v>64859494</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spånsmyran, Dlr</t>
+          <t>Omr.26 Öster, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506832.7001705997</v>
+        <v>507013</v>
       </c>
       <c r="R2" t="n">
-        <v>6692583.750383312</v>
+        <v>6692634</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,70 +763,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lars-Erik Nilsson, Uno Skog, Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110215717</v>
+        <v>65025737</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spånsmyran, Dlr</t>
+          <t>Öster Vittberget, SV Stora Spånsan, område 26, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507105.1793649141</v>
+        <v>507014</v>
       </c>
       <c r="R3" t="n">
-        <v>6692596.144183958</v>
+        <v>6692635</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,76 +860,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Urban Gunnarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Urban Gunnarsson, Janolof Hermansson, Johanne Maad, Lars-Erik Nilsson, Uno Skog, Stig-Åke Svenson, Olov Tranberg, Matilda Elgerud, Bonnie Nilzon, Staffan Jansson, Bo karlstens, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110217134</v>
+        <v>95758673</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spånsmyran, Dlr</t>
+          <t>Fäbodmyran N, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506876.8671243503</v>
+        <v>507392</v>
       </c>
       <c r="R4" t="n">
-        <v>6692546.240383792</v>
+        <v>6692335</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,76 +965,76 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110215976</v>
+        <v>119925031</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spånsmyran, Dlr</t>
+          <t>Stora Spånsan, Stora Spånsan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507027.9654846591</v>
+        <v>506622</v>
       </c>
       <c r="R5" t="n">
-        <v>6692555.927691584</v>
+        <v>6692840</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1058,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,80 +1088,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112736301</v>
+        <v>64858793</v>
       </c>
       <c r="B6" t="n">
-        <v>55964</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spånsmyran (Spånsmyran), Dlr</t>
+          <t>Omr.26 StorOlles- St. Spånsan Öster, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506905</v>
+        <v>507351</v>
       </c>
       <c r="R6" t="n">
-        <v>6692589</v>
+        <v>6692388</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,12 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1187,1779 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>65025652</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster Vittberget, SV Stora Spånsan, område 26, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>507349</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6692361</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson, Janolof Hermansson, Johanne Maad, Lars-Erik Nilsson, Uno Skog, Stig-Åke Svenson, Olov Tranberg, Matilda Elgerud, Bonnie Nilzon, Staffan Jansson, Bo karlstens, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95758701</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäbodmyran N, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>506922</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6692528</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96048868</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fäbodmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>507048</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692393</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119925224</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Spånsan, Stora Spånsan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506661</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6692775</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>64882770</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Omr.26 Öster, Vittberget SV om Stora Spånsan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>507161</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6692659</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blockigt mot Stora Spånsan</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stump # kolad ved på kort naturlig stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Andreas Öster, Stig-Åke Svenson, Urban Gunnarsson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>65025686</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster Vittberget, SV Stora Spånsan, område 26, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>507078</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6692431</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson, Janolof Hermansson, Johanne Maad, Lars-Erik Nilsson, Uno Skog, Stig-Åke Svenson, Olov Tranberg, Matilda Elgerud, Bonnie Nilzon, Staffan Jansson, Bo karlstens, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64859438</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Omr.26 Öster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>506980</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6692543</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Betad tall, spillning.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112736301</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506904</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6692590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110215717</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>507105</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6692596</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110215976</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>507027</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6692556</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110216272</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>507006</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6692519</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110216939</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506833</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6692583</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95796425</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fäbodmyran N, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>507107</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6692413</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110217134</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Spånsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506877</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6692546</v>
+      </c>
+      <c r="S20" t="n">
+        <v>18</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>64882826</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Omr.26 Öster, Vittberget SV om Stora Spånsan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>507161</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6692659</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>blockigt mot Stora Spånsan</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stump # kolad ved på kort naturlig stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Andreas Öster, Stig-Åke Svenson, Urban Gunnarsson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>64882743</v>
+      </c>
+      <c r="B22" t="n">
+        <v>81332</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229436</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Halmgul örnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ochrolechia alboflavescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Wulfen) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Omr.26 Öster, Vittberget SV om Stora Spånsan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>507161</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6692659</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>blockigt mot Stora Spånsan</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>gammalt träd med grova torrgrenar</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dead branch  # barklös gren # Picea abies # gammalt träd med grova torrgrenar</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Andreas Öster, Stig-Åke Svenson, Urban Gunnarsson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59665-2022 artfynd.xlsx
+++ b/artfynd/A 59665-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -776,6 +781,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64859494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65025737</t>
         </is>
       </c>
     </row>
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95758673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119925031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64858793</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65025652</t>
         </is>
       </c>
     </row>
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95758701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96048868</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119925224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64882770</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65025686</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64859438</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112736301</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110215717</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110215976</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110216272</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,6 +2562,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110216939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2587,6 +2677,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95796425</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2689,6 +2784,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110217134</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64882826</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2960,8 +3065,36 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64882743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>